--- a/viewer/downloads/Grade_7_MN2022_Alignment.xlsx
+++ b/viewer/downloads/Grade_7_MN2022_Alignment.xlsx
@@ -487,7 +487,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,12 +553,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>CC2 8.2.1 (Representative Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 8.2.1 (Representative Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>CC2 11.2.3 (); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 11.2.3 (); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>CC2 11.2.3 (); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 11.2.3 (); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples); CC2 9.2.1 (Surface Area and Volumne)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>CC2 9.3.1 CL ()</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 9.3.1 CL ()</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>CC2 10.1.1 (); CC2 9.3.1 CL ()</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 10.1.1 (); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 9.3.1 CL ()</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>CC2 11.2.3 (); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 11.2.3 (); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions); CC2 8.2.1 (Representative Samples); CC2 8.2.2 (Inference from Random Samples)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>CC2 1.2.1 (Probability); CC2 1.2.2 (Probability); CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
-Dec)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.1 (Probability); CC2 1.2.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
+Dec); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -778,13 +778,13 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>CC2 1.2.1 (Probability); CC2 1.2.2 (Probability); CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
-Dec)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.1 (Probability); CC2 1.2.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
+Dec); CC2 5.2.1 (Probability); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>CC2 1.2.7 (Compound Probability); CC2 1.2.8 (Compound Probability); CC2 5.2.3 (Compound Independent Events); CC2 5.2.6 (Compound Events)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 1.2.7 (Compound Probability); CC2 1.2.8 (Compound Probability); CC2 5.2.1 (Probability); CC2 5.2.3 (Compound Independent Events); CC2 5.2.6 (Compound Events); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>CC2 5.2.4 (Probability Tables); CC2 5.2.5 (Probability Trees)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 5.2.1 (Probability); CC2 5.2.4 (Probability Tables); CC2 5.2.5 (Probability Trees); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>CC2 5.2.2 (Computer Simulations of Probab)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 5.2.1 (Probability); CC2 5.2.2 (Computer Simulations of Probab); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>CC2 5.2.2 (Computer Simulations of Probab); CC2 5.2.4 (Probability Tables); CC2 5.2.5 (Probability Trees)</t>
+          <t>CC2 1.1.2 (Probability); CC2 1.2.3 (Probability); CC2 1.2.5 (Probability); CC2 5.2.1 (Probability); CC2 5.2.2 (Computer Simulations of Probab); CC2 5.2.4 (Probability Tables); CC2 5.2.5 (Probability Trees); CC2 8.1.2 (Comparing Distributions)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation_supplement</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation_supplement</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,13 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>CC2 10.2.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 10.2.1 (); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -971,12 +972,13 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>CC2 10.2.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 10.2.1 (); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1005,13 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>CC2 10.2.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 10.2.1 (); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1038,13 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>CC2 10.2.1 (); CC2 10.3.3 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 10.2.1 (); CC2 10.3.3 (); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1071,13 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>CC2 6.1.1 (Comparing Expressions); CC2 6.1.3 (Solve one-variable inequalitie); CC2 6.2.3 (solving equations with recorde)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 6.1.1 (Comparing Expressions); CC2 6.1.3 (Solve one-variable inequalitie); CC2 6.2.3 (solving equations with recorde); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1104,13 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.1.1 (Identifying Proportionality in); CC2 4.1.2 (Determining Scale Factors)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.1.1 (Identifying Proportionality in); CC2 4.1.2 (Determining Scale Factors); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1137,13 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.4.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.4.1 (); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1170,13 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.1.1 (Identifying Proportionality in); CC2 4.1.2 (Determining Scale Factors); CC2 4.4.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.1.1 (Identifying Proportionality in); CC2 4.1.2 (Determining Scale Factors); CC2 4.4.1 (); CC2 9.1.1 (Circumference, Diameter, and P); CC2 9.1.2 (area of circles); CC2 9.1.3 (Area of Composite Shapes); CC2 9.2.2 (Cross Sections); CC2 9.2.3 (Volume of Prsms); CC2 9.2.4 (Volume of Non-Rectangular Pris); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1195,13 +1203,14 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
-Dec)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.1.1 (Repeating and Terminating Deci); CC2 2.1.2 (Making Connections between
+Dec); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1237,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>CC2 2.2.2 (Integer Operations and Zero Pi); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 2.2.4 (Understanding Multiuplication )</t>
+          <t>CC2 1.1.5 (Rational numbers and decimals); CC2 2.2.2 (Integer Operations and Zero Pi); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 2.2.4 (Understanding Multiuplication ); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 7.1.3 (Solving Problems Involving Per)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1269,13 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>CC2 7.1.1 (Distance, Rate, and Time); CC2 7.1.4 (Equations with Fraction and De)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 7.1.1 (Distance, Rate, and Time); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.4 (Equations with Fraction and De); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1302,13 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>CC2 3.2.1 (Subtracting Integers); CC2 3.2.3 (Understanding Multiplication a)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.1 (Subtracting Integers); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.3 (Understanding Multiplication a); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1335,13 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>CC2 2.2.1 (Integer Operations); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 3.2.1 (Subtracting Integers); CC2 3.2.5 (Evaluating Expressions with In); CC2 5.1.1 (Part-Whole Relationships); CC2 5.1.2 (Finding and Using Percentages)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.1 (Integer Operations); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.1 (Subtracting Integers); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.2.5 (Evaluating Expressions with In); CC2 3.3.2 (Dividing Decimals); CC2 5.1.1 (Part-Whole Relationships); CC2 5.1.2 (Finding and Using Percentages); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1356,13 +1368,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>CC2 2.2.2 (Integer Operations and Zero Pi); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 3.1.1 (Order of Operations
-Distributi); CC2 3.3.3 (Simplifying Expressions)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.2 (Integer Operations and Zero Pi); CC2 2.2.3 (Integer Operations and Zero Pi); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.1.1 (Order of Operations
+Distributi); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 3.3.3 (Simplifying Expressions); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1404,13 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.1.1 (Identifying Proportionality in); CC2 4.2.3 (Determining Proportionality an); CC2 4.4.1 ()</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.2.6 (Fraction Addition); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.1.1 (Identifying Proportionality in); CC2 4.2.3 (Determining Proportionality an); CC2 4.4.1 (); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1437,15 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.3.1 (Combining Like Terms); CC2 4.3.3 (Simplifying Algebraice Express)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 4.3.1 (Combining Like Terms); CC2 4.3.2 (Using the Distributive Propert); CC2 4.3.3 (Simplifying Algebraice Express); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1472,15 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>CC2 7.1.4 (Equations with Fraction and De); CC2 7.2.1 (Finding Missing Information in); CC2 8.1.1 (Measurement Precision)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.4 (Equations with Fraction and De); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.1 (Finding Missing Information in); CC2 7.2.2 (Solving Proportions); CC2 8.1.1 (Measurement Precision); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1507,15 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>CC2 3.1.2 (Evaluating Expresisons); CC2 3.2.1 (Subtracting Integers)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 1.2.6 (Fraction Addition); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.1.2 (Evaluating Expresisons); CC2 3.2.1 (Subtracting Integers); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.5 (Creating Integer Coefficients); CC2 7.1.6 (Creating Integer Coefficients ); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1542,15 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>CC2 5.1.1 (Part-Whole Relationships); CC2 5.1.2 (Finding and Using Percentages); CC2 8.1.1 (Measurement Precision); CC2 8.2.2 (Inference from Random Samples)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 1.1.5 (Rational numbers and decimals); CC2 2.2.5 (Multiplication of Rational Num); CC2 2.2.6 (Multiplying of Mixed Numbers); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 3.2.2 (Adding and Subtracting Integer); CC2 3.2.4 (Multiplying Decimals); CC2 3.3.2 (Dividing Decimals); CC2 4.3.2 (Using the Distributive Propert); CC2 5.1.1 (Part-Whole Relationships); CC2 5.1.2 (Finding and Using Percentages); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.3 (Solving Problems Involving Per); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC2 8.1.1 (Measurement Precision); CC2 8.2.2 (Inference from Random Samples); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1577,14 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>CC2 3.2.5 (Evaluating Expressions with In); CC2 3.3.1 (Dividing with Rational Numbers); CC2 3.3.3 (Simplifying Expressions); CC2 8.1.1 (Measurement Precision)</t>
+          <t>CC2 3.2.5 (Evaluating Expressions with In); CC2 3.3.1 (Dividing with Rational Numbers); CC2 3.3.3 (Simplifying Expressions); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC2 8.1.1 (Measurement Precision); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1611,15 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.2.2 (Creating and Identifying Propo); CC2 4.2.4 (Making Connections with Propor)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.2.2 (Creating and Identifying Propo); CC2 4.2.4 (Making Connections with Propor); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1647,15 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.2.1 (Understanding Proportional and); CC2 4.2.4 (Making Connections with Propor)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.2.1 (Understanding Proportional and); CC2 4.2.4 (Making Connections with Propor); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.1.2 (Comparing Expressions with Var); CC2 6.1.4 (Solve one-variable inequalitie); CC2 6.2.1 (Solving Equations); CC2 6.2.2 (Solving Equations and the Dist); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, bridged_via_content, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1682,15 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>CC2 4.2.2 (Creating and Identifying Propo); CC2 4.2.4 (Making Connections with Propor)</t>
+          <t>CC2 1.1.4 (Proportional Reasoning); CC2 2.3.1 (Graphing Points on a Coordinat); CC2 2.3.2 (Graphing Points on a Coordinat); CC2 4.2.2 (Creating and Identifying Propo); CC2 4.2.4 (Making Connections with Propor); CC2 4.3.2 (Using the Distributive Propert); CC2 5.3.1 (Describing Relationships Betwe); CC2 5.3.2 (Solving Word Problems); CC2 5.3.3 (Solving Word Problems); CC2 5.3.4 (Solving Word Problems with Var); CC2 5.3.5 (Solving Word Problems with Var); CC2 6.2.4 (Writing equations from Word Pr); CC2 6.2.5 (Writing and Solving Equations); CC2 7.1.7 (Percent Increase and Decrease); CC2 7.1.8 (Simple Interest); CC2 7.2.2 (Solving Proportions); CC3 1.2.2 (Equivalent Ratios
+Solving Prop); CC3 2.1.1 (Area
+Simplyfiing Expressions); CC3 2.1.3 (Simplifying Algebraic Expressi); CC3 2.1.6 (Inequalities
+Simplifying Agle)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>mn_correlation</t>
+          <t>bridged_via_ccss, mn_correlation</t>
         </is>
       </c>
     </row>
